--- a/data/trans_bre/IP42B-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP42B-Habitat-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 12,06</t>
+          <t>-5,04; 13,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 15,41</t>
+          <t>-9,62; 14,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,06; 4,28</t>
+          <t>-14,16; 4,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-64,92; 367,71</t>
+          <t>-68,76; 357,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-87,49; 91,43</t>
+          <t>-88,66; 92,43</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 13,92</t>
+          <t>-4,9; 13,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 17,34</t>
+          <t>-5,24; 17,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 7,36</t>
+          <t>-7,55; 6,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-67,46; inf</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 293,48</t>
+          <t>-34,52; 238,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-65,08; 172,58</t>
+          <t>-68,05; 166,52</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 11,93</t>
+          <t>-14,15; 13,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 11,96</t>
+          <t>-17,85; 11,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 13,96</t>
+          <t>-2,39; 13,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-80,59; 304,73</t>
+          <t>-78,37; 365,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,13; 88,91</t>
+          <t>-54,4; 78,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-53,29; 1087,0</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 11,29</t>
+          <t>-9,81; 10,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 11,77</t>
+          <t>-12,01; 11,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 13,58</t>
+          <t>-4,63; 12,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-77,62; 257,24</t>
+          <t>-73,16; 179,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,02; 178,74</t>
+          <t>-66,6; 157,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,92; 657,15</t>
+          <t>-56,18; 434,11</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 6,95</t>
+          <t>-3,06; 7,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 8,27</t>
+          <t>-4,45; 7,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 4,9</t>
+          <t>-3,02; 5,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-34,47; 136,04</t>
+          <t>-33,99; 141,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,22; 78,12</t>
+          <t>-26,24; 65,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,48; 79,35</t>
+          <t>-34,51; 102,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP42B-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP42B-Habitat-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 13,28</t>
+          <t>-5,5; 11,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 14,18</t>
+          <t>-8,72; 14,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 4,88</t>
+          <t>-13,45; 5,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-68,76; 357,97</t>
+          <t>-69,67; 325,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-88,66; 92,43</t>
+          <t>-85,86; 107,45</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 13,94</t>
+          <t>-5,0; 12,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 17,83</t>
+          <t>-5,41; 16,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 6,39</t>
+          <t>-7,25; 7,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-67,46; inf</t>
+          <t>-74,62; 735,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 238,45</t>
+          <t>-39,76; 238,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,05; 166,52</t>
+          <t>-68,39; 208,74</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 13,25</t>
+          <t>-12,46; 13,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 11,52</t>
+          <t>-17,24; 10,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 13,28</t>
+          <t>-1,88; 13,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-78,37; 365,92</t>
+          <t>-73,04; 389,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-54,4; 78,61</t>
+          <t>-56,3; 69,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,29; 1087,0</t>
+          <t>-55,67; 945,72</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 10,78</t>
+          <t>-9,13; 12,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 11,17</t>
+          <t>-12,79; 10,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 12,94</t>
+          <t>-4,74; 13,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-73,16; 179,47</t>
+          <t>-70,21; 289,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,6; 157,4</t>
+          <t>-72,08; 147,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,18; 434,11</t>
+          <t>-54,98; 512,59</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 7,05</t>
+          <t>-3,26; 6,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 7,65</t>
+          <t>-4,14; 8,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 5,43</t>
+          <t>-2,95; 5,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-33,99; 141,77</t>
+          <t>-35,8; 141,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,24; 65,4</t>
+          <t>-24,52; 75,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,51; 102,89</t>
+          <t>-32,07; 107,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP42B-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP42B-Habitat-trans_bre.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 11,64</t>
+          <t>-5,16; 12,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 14,61</t>
+          <t>-9,46; 15,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 5,01</t>
+          <t>-14,06; 4,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -654,12 +654,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-69,67; 325,52</t>
+          <t>-64,92; 367,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-85,86; 107,45</t>
+          <t>-87,49; 91,43</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 12,6</t>
+          <t>-4,3; 13,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 16,08</t>
+          <t>-4,23; 17,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 7,53</t>
+          <t>-7,25; 7,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-74,62; 735,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,76; 238,2</t>
+          <t>-28,68; 293,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,39; 208,74</t>
+          <t>-65,08; 172,58</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 13,91</t>
+          <t>-14,15; 11,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 10,67</t>
+          <t>-17,16; 11,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 13,19</t>
+          <t>-1,66; 13,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-73,04; 389,06</t>
+          <t>-80,59; 304,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-56,3; 69,62</t>
+          <t>-55,13; 88,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-55,67; 945,72</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 12,35</t>
+          <t>-10,32; 11,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 10,62</t>
+          <t>-13,06; 11,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 13,1</t>
+          <t>-3,89; 13,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-70,21; 289,82</t>
+          <t>-77,62; 257,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-72,08; 147,76</t>
+          <t>-68,02; 178,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,98; 512,59</t>
+          <t>-52,92; 657,15</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 6,83</t>
+          <t>-3,07; 6,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 8,18</t>
+          <t>-4,12; 8,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 5,68</t>
+          <t>-3,38; 4,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-35,8; 141,98</t>
+          <t>-34,47; 136,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 75,67</t>
+          <t>-26,22; 78,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 107,39</t>
+          <t>-34,48; 79,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP42B-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP42B-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,155 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,11</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-4,54</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>44,15%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>21,56%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-40,13%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.611531059921378</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.109565092295412</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-4.539265982861636</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.4415314655282406</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.2155880866218702</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.4013354059539014</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-5,16; 12,06</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-9,46; 15,41</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-14,06; 4,28</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-64,92; 367,71</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-87,49; 91,43</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.160171189539602</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-9.457198324186297</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-14.06133528781276</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="n">
+        <v>-0.6491597382145311</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.8748560861650793</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>12.05881951408033</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>15.40713955788545</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4.277144868842229</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="n">
+        <v>3.67712065090506</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.9143115031625317</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4,54</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5,85</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>92,58%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>51,51%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-3,94%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-4,3; 13,92</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,23; 17,34</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-7,25; 7,36</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-28,68; 293,48</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-65,08; 172,58</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>4.54082753915843</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>5.848626547383169</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.3095949453775268</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.9258426955879854</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.5151482689059161</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.03937030911739987</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,56</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,46</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,36</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-10,56%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>137,26%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-4.30188774305917</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.232738923843285</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-7.24864777853538</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n">
+        <v>-0.2868288926031353</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.6507796979382783</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-14,15; 11,93</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-17,16; 11,96</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,66; 13,96</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-80,59; 304,73</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-55,13; 88,91</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>13.91985352622176</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>17.34467530058024</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>7.356467121379271</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="n">
+        <v>2.934778957803852</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.725775007548129</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +759,239 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,2</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3,93</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-3,35%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-8,89%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>62,51%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.555633270154031</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.45533036775491</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>5.359946702110314</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.0517002242958387</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.1056138833711755</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1.372618546535836</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-10,32; 11,29</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-13,06; 11,77</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,89; 13,58</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-77,62; 257,24</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-68,02; 178,74</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-52,92; 657,15</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-14.1512134642526</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-17.15766657828152</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.660727986783002</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.8059453759062924</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5512981738022125</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>11.93186469412456</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>11.96446406289102</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>13.96341227724437</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>3.047300668125036</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.8890969133294715</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.3462485504695384</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.197854855816649</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>3.930353914168427</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.03348033257278159</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.08894850146180504</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.6251029767542011</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-10.31947793335229</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-13.05620193491748</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.890881222297109</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.7761835054548785</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.6801551254036537</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5291907700511126</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>11.293751810022</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>11.77372522364906</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>13.58492185162262</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>2.572404067467021</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.787383969310088</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>6.571486695252591</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,76</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>25,55%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-3,07; 6,95</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-4,12; 8,27</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-3,38; 4,9</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-34,47; 136,04</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-26,22; 78,12</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-34,48; 79,35</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>1.869401378026056</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.756605808189621</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.9371912646043784</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.2555066936809234</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.1251437078747213</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.1251257214923607</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-3.066655213804931</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-4.115552503575893</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.381218104972041</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.3447460209054771</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2622286282783215</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3447813496249396</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>6.949389186567315</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>8.269951233547307</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.899031766782712</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>1.360435599647229</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.7811743054328715</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.7934584600859568</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +1000,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
